--- a/pensum/ok02/OK02_Klasseoppgaver_v5.xlsx
+++ b/pensum/ok02/OK02_Klasseoppgaver_v5.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="158">
   <si>
     <t xml:space="preserve">Klasseoppgaver til Økonomistyring kapittel 2: Viktige bedriftsøkonomiske begreper (V5)</t>
   </si>
@@ -140,18 +140,48 @@
     <t xml:space="preserve">a)  Varekostnaden i april, i kroner: lager ved starten av april pluss varekjøpet i april minus lager ved slutten av april.</t>
   </si>
   <si>
+    <t xml:space="preserve">Formel og begrep</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Varekostnad = varebeholdning (IB) + varekjøp − varebeholdning (UB) (Økonomistyring 2.2.1).</t>
+  </si>
+  <si>
     <t xml:space="preserve">b)  Hvor mye går ut av kontoen til Polarlys i april? Husk 30 dagers kreditt.</t>
   </si>
   <si>
+    <t xml:space="preserve">Utbetaling = innfrielse av en betalingsforpliktelse; utgift = anskaffelsen som skaper forpliktelsen (Økonomistyring 2.2.1).</t>
+  </si>
+  <si>
     <t xml:space="preserve">c)  Legg sammen for mars, april og mai. Hvor mye mer gikk ut av kontoen til Polarlys enn det som ble varekostnad? Regn sum utbetalt minus sum varekostnad.</t>
   </si>
   <si>
+    <t xml:space="preserve">Samme tre begreper over flere måneder (Økonomistyring 2.2.1). Over en periode er sum kostnad = sum utgift + nedgang i lageret, og sum utbetaling = sum utgift + nedgang i leverandørgjelden.</t>
+  </si>
+  <si>
     <t xml:space="preserve">d)  Ida regner varekostnaden i mai som lager før minus lager etter: 1 380 000 − 1 100 000 = 280 000 kr. Hva er feil?   A: Ingenting. Varekostnaden er endringen i lageret   B: Varekjøpet i mai mangler. Riktig er 1 380 000 + 520 000 − 1 100 000 = 800 000   C: Hun skulle brukt utbetalingen i mai, 640 000   (skriv bokstaven)</t>
   </si>
   <si>
     <t xml:space="preserve">e)  Kari sier: «Regnskapet viste overskudd i april, men kontoen var trang.» Forklar hvordan det kan henge sammen med utgift, utbetaling og kostnad, og foreslå ett tiltak. To–tre setninger.</t>
   </si>
   <si>
+    <t xml:space="preserve">Ingen ny formel. Utgift, utbetaling og kostnad (Økonomistyring 2.2.1); likviditetsbudsjettet kommer i kap. 9.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hint, hvis du står fast</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lageret ved start</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lageret ved starten av april er lageret ved slutten av mars: 1 460 000. Varekostnad = lager ved start + varekjøp − lager ved slutt.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kreditten</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30 dagers kreditt: det dere betaler i april, er det dere kjøpte i mars. Utbetalingen i mai er aprilkjøpet.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Kilde: Hjertnes, J. og Skorpen, K.: Økonomistyring for LØM-emnet, kap. 2, avsnitt 2.2.1 (utgift, utbetaling, kostnad og varekostnadsformelen). Nordlys Elektro AS er en konstruert casebedrift.</t>
   </si>
   <si>
@@ -212,12 +242,21 @@
     <t xml:space="preserve">a)  Sum faste kostnader utenom lønn for året, i kroner: avskrivning på utstyret, andre driftskostnader og renter på banklånet.</t>
   </si>
   <si>
+    <t xml:space="preserve">Faste kostnader (kapasitetskostnader): avskrivninger, finanskostnader, husleie m.m. (Økonomistyring 2.2.2). Lineær avskrivning = anskaffelseskost / levetid (2.4.3).</t>
+  </si>
+  <si>
     <t xml:space="preserve">b)  Faste kostnader utenom lønn per fakturerbar time, i hele kroner, når dere fakturerer 3 500 timer.</t>
   </si>
   <si>
+    <t xml:space="preserve">Faste kostnader per enhet = faste totale kostnader / antall produserte enheter (Økonomistyring 2.2.2). Her er enheten en fakturerbar time.</t>
+  </si>
+  <si>
     <t xml:space="preserve">c)  Hva blir faste kostnader utenom lønn per fakturerbar time hvis dere bare fakturerer 3 000 timer? Hele kroner.</t>
   </si>
   <si>
+    <t xml:space="preserve">Faste kostnader per enhet = faste totale kostnader / antall enheter. Lav produksjonsmengde gir høye faste kostnader per enhet (Økonomistyring 2.2.2, figur 2.3).</t>
+  </si>
+  <si>
     <t xml:space="preserve">d)  Er dette en fast kostnad for Fjell Elektro? Spør for hver post: forsvinner kostnaden hvis dere sier nei til en jobb?</t>
   </si>
   <si>
@@ -242,6 +281,21 @@
     <t xml:space="preserve">e)  Montørene har fast månedslønn. Er lønna deres en fast eller en variabel kostnad, og hva bør eieren gjøre i en stille måned? To–tre setninger.</t>
   </si>
   <si>
+    <t xml:space="preserve">Lønnskostnader er faste på kort sikt; administrasjonslønn er fast, produksjonslønn varierer med produksjonsmengden (Økonomistyring 2.2.2).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hva er fast?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spør for hver post: forsvinner den hvis vi sier nei til jobben? Avskrivning 300 000 / 5. Renter 500 000 × 7,5 %. Lønna holder dere utenfor i a–c.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Per time</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Del summen på antall fakturerbare timer. Samme kroner, færre timer: hver time må bære mer.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Kilde: Hjertnes, J. og Skorpen, K.: Økonomistyring for LØM-emnet, kap. 2, avsnitt 2.2.2 (faste og variable kostnader, faste kostnader per enhet) og 2.4.3 (avskrivninger). Fjell Elektro AS er en konstruert casebedrift.</t>
   </si>
   <si>
@@ -290,12 +344,21 @@
     <t xml:space="preserve">a)  Sum direkte kostnader for jobben, i kroner: materiell, montørtimer og kjøring.</t>
   </si>
   <si>
+    <t xml:space="preserve">Direkte materialkostnad = antall enheter × pris per enhet. Direkte lønnskostnad = timer × timesats. Kjøring er en annen direkte kostnad (Økonomistyring 2.2.3).</t>
+  </si>
+  <si>
     <t xml:space="preserve">b)  Selvkosten for jobben, i kroner: direkte kostnader pluss den indirekte andelen, 267 kr per montørtime.</t>
   </si>
   <si>
+    <t xml:space="preserve">Selvkost (STK) = direkte kostnader + jobbens andel av de indirekte kostnadene (Økonomistyring 2.2.3 og 2.3). Fordelingen med sats per time kommer i kap. 5.</t>
+  </si>
+  <si>
     <t xml:space="preserve">c)  Fortjenesten på jobben, i kroner: salgsinntekt minus selvkost.</t>
   </si>
   <si>
+    <t xml:space="preserve">Fortjeneste = sum totale inntekter (STI) − sum totale kostnader (STK), og STI = P × M (Økonomistyring 2.3).</t>
+  </si>
+  <si>
     <t xml:space="preserve">d)  Er dette en direkte kostnad for ladepunktjobben? Spør: kan kostnaden knyttes til akkurat denne jobben?</t>
   </si>
   <si>
@@ -320,6 +383,21 @@
     <t xml:space="preserve">e)  Se på fortjenesten du fant i c, i prosent av prisen. Hva er usikkert i kalkylen, og hva skal Kari se etter før hun sier ja? To–tre setninger.</t>
   </si>
   <si>
+    <t xml:space="preserve">Ingen ny formel. Direkte og indirekte kostnader og selvkost (Økonomistyring 2.2.3 og 2.3).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Direkte kostnader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Seks ladepunkter: materiell 6 × 6 500. To timer per ladepunkt: 12 timer × 640. Kjøringen én gang. Det indirekte kommer i b.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Strømmen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spør: kan kostnaden knyttes til akkurat denne jobben? Strømmen varierer med aktiviteten, men den kan ikke knyttes til borettslaget.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Kilde: Hjertnes, J. og Skorpen, K.: Økonomistyring for LØM-emnet, kap. 2, avsnitt 2.2.3 (direkte og indirekte kostnader, kalkyleobjekt, håndverksbedrift) og 2.3.1 (fortjeneste = STI − STK). Fordeling av indirekte kostnader: kap. 5. Nordlys Elektro AS er en konstruert casebedrift.</t>
   </si>
   <si>
@@ -365,12 +443,21 @@
     <t xml:space="preserve">a)  Lønnskostnaden for montøren for ett år, i kroner, med bokas 46,8 % sosiale kostnader.</t>
   </si>
   <si>
+    <t xml:space="preserve">Lønnskostnad = brutto lønn × (1 + sats for sosiale kostnader). Bokas tabell 2.4: 46,8 % (Økonomistyring 2.4.1).</t>
+  </si>
+  <si>
     <t xml:space="preserve">b)  Montøren er 61 år og får 14,3 % feriepenger. Feriepenger inkludert arbeidsgiveravgift blir da 16,3 % i stedet for 13,7 %. Hva blir lønnskostnaden?</t>
   </si>
   <si>
+    <t xml:space="preserve">Feriepenger 12 % under 60 år og 14,3 % fra 60 år (Økonomistyring 2.4.1). Med arbeidsgiveravgift: 12 × 1,141 = 13,7 % og 14,3 × 1,141 = 16,3 %.</t>
+  </si>
+  <si>
     <t xml:space="preserve">c)  Fjell velger minstekravet for obligatorisk tjenestepensjon: 2 % pensjon og 0,3 % arbeidsgiveravgift på pensjon, i stedet for bokas 8,0 % og 1,1 %. Hva blir lønnskostnaden (montør under 60)?</t>
   </si>
   <si>
+    <t xml:space="preserve">Pensjonspremie minimum 2 % OTP (Økonomistyring 2.4.1; lov om obligatorisk tjenestepensjon § 4). Tabell 2.4 bruker 8,0 % pensjon og 1,1 % arbeidsgiveravgift på pensjon.</t>
+  </si>
+  <si>
     <t xml:space="preserve">d)  Hører dette med i de sosiale kostnadene på lønna (bokas tabell 2.4)?</t>
   </si>
   <si>
@@ -393,6 +480,21 @@
   </si>
   <si>
     <t xml:space="preserve">e)  Eieren vil sette timeprisen ut fra montørens timelønn: 560 000 / 1 800 betalte timer = 311 kr. Hva sier du til ham? Bruk lønnskostnaden fra a og de fakturerbare timene.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lønnskostnad per time = lønnskostnad / timer. Lønnskostnaden fra a); fordelingen på fakturerbare timer er timepriskalkylen i kap. 5.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ny prosent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Start med 46,8 %. Trekk fra posten som endres, legg til den nye: 46,8 − 13,7 + 16,3. Gang så lønna med 1 + den nye prosenten.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Timeprisen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lønnskostnad delt på betalte timer, så på fakturerbare timer. De 400 timene er betalt gjennom lønna, men kunden betaler ikke for dem.</t>
   </si>
   <si>
     <t xml:space="preserve">Kilde: Hjertnes, J. og Skorpen, K.: Økonomistyring for LØM-emnet, kap. 2, avsnitt 2.4 og 2.4.1 med tabell 2.4 (sosiale kostnader 46,8 %). Pensjon minst 2 %: lov om obligatorisk tjenestepensjon § 4. Arbeidsgiveravgift 14,1 % i sone I (Skatteetaten). Ikke-fakturerbar tid i timepriskalkylen: kap. 5. Fjell Elektro AS er en konstruert casebedrift.</t>
@@ -406,7 +508,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="#,##0.##;\−#,##0.##;\0"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="13">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -473,8 +575,30 @@
       <family val="0"/>
       <charset val="1"/>
     </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
+      <color rgb="FF2F4A6D"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -496,7 +620,25 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF4F6FA"/>
-        <bgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFEEF2F8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEEF2F8"/>
+        <bgColor rgb="FFF4F6FA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB8954A"/>
+        <bgColor rgb="FF808080"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBF6EA"/>
+        <bgColor rgb="FFF4F6FA"/>
       </patternFill>
     </fill>
   </fills>
@@ -549,7 +691,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="29">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -626,11 +768,31 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -675,8 +837,8 @@
       <rgbColor rgb="FF808080"/>
       <rgbColor rgb="FF9999FF"/>
       <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FFF4F6FA"/>
-      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FFFBF6EA"/>
+      <rgbColor rgb="FFEEF2F8"/>
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
       <rgbColor rgb="FF0066CC"/>
@@ -690,7 +852,7 @@
       <rgbColor rgb="FF008080"/>
       <rgbColor rgb="FF0000FF"/>
       <rgbColor rgb="FF00CCFF"/>
-      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FFF4F6FA"/>
       <rgbColor rgb="FFCCFFCC"/>
       <rgbColor rgb="FFFFFF99"/>
       <rgbColor rgb="FF99CCFF"/>
@@ -704,7 +866,7 @@
       <rgbColor rgb="FFFF9900"/>
       <rgbColor rgb="FFFF6600"/>
       <rgbColor rgb="FF5E6670"/>
-      <rgbColor rgb="FF969696"/>
+      <rgbColor rgb="FFB8954A"/>
       <rgbColor rgb="FF003366"/>
       <rgbColor rgb="FF339966"/>
       <rgbColor rgb="FF003300"/>
@@ -1007,7 +1169,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:G38"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34"/>
@@ -1160,35 +1322,20 @@
         <v/>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="7" t="s">
+    <row r="17" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="19" t="s">
         <v>38</v>
       </c>
-      <c r="B17" s="7"/>
-      <c r="C17" s="7"/>
-      <c r="D17" s="7"/>
-      <c r="E17" s="7"/>
-      <c r="F17" s="12"/>
-      <c r="G17" s="18" t="str">
-        <f aca="false">IF(F17="","",IF(ABS(F17-(890000))&lt;=0.000000001,"Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="7" t="s">
+      <c r="B17" s="20" t="s">
         <v>39</v>
       </c>
-      <c r="B18" s="7"/>
-      <c r="C18" s="7"/>
-      <c r="D18" s="7"/>
-      <c r="E18" s="7"/>
-      <c r="F18" s="12"/>
-      <c r="G18" s="18" t="str">
-        <f aca="false">IF(F18="","",IF(ABS(F18-(90000))&lt;=0.000000001,"Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C17" s="20"/>
+      <c r="D17" s="20"/>
+      <c r="E17" s="20"/>
+      <c r="F17" s="20"/>
+      <c r="G17" s="20"/>
+    </row>
+    <row r="19" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="7" t="s">
         <v>40</v>
       </c>
@@ -1196,84 +1343,195 @@
       <c r="C19" s="7"/>
       <c r="D19" s="7"/>
       <c r="E19" s="7"/>
-      <c r="F19" s="19"/>
+      <c r="F19" s="12"/>
       <c r="G19" s="18" t="str">
-        <f aca="false">IF(F19="","",IF(UPPER(TRIM(F19))="B","Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="7" t="s">
+        <f aca="false">IF(F19="","",IF(ABS(F19-(890000))&lt;=0.000000001,"Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="B20" s="20" t="s">
         <v>41</v>
       </c>
-      <c r="B20" s="7"/>
-      <c r="C20" s="7"/>
-      <c r="D20" s="7"/>
-      <c r="E20" s="7"/>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="20"/>
-      <c r="B21" s="20"/>
-      <c r="C21" s="20"/>
-      <c r="D21" s="20"/>
-      <c r="E21" s="20"/>
-      <c r="F21" s="20"/>
-      <c r="G21" s="20"/>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="20"/>
-      <c r="B22" s="20"/>
-      <c r="C22" s="20"/>
-      <c r="D22" s="20"/>
-      <c r="E22" s="20"/>
-      <c r="F22" s="20"/>
-      <c r="G22" s="20"/>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="20"/>
-      <c r="B23" s="20"/>
+      <c r="C20" s="20"/>
+      <c r="D20" s="20"/>
+      <c r="E20" s="20"/>
+      <c r="F20" s="20"/>
+      <c r="G20" s="20"/>
+    </row>
+    <row r="22" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="B22" s="7"/>
+      <c r="C22" s="7"/>
+      <c r="D22" s="7"/>
+      <c r="E22" s="7"/>
+      <c r="F22" s="12"/>
+      <c r="G22" s="18" t="str">
+        <f aca="false">IF(F22="","",IF(ABS(F22-(90000))&lt;=0.000000001,"Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="B23" s="20" t="s">
+        <v>43</v>
+      </c>
       <c r="C23" s="20"/>
       <c r="D23" s="20"/>
       <c r="E23" s="20"/>
       <c r="F23" s="20"/>
       <c r="G23" s="20"/>
     </row>
-    <row r="25" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B25" s="6"/>
-      <c r="C25" s="6"/>
-      <c r="D25" s="6"/>
-      <c r="E25" s="6"/>
-      <c r="F25" s="6"/>
-      <c r="G25" s="6"/>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B26" s="6"/>
-      <c r="C26" s="6"/>
-      <c r="D26" s="6"/>
-      <c r="E26" s="6"/>
-      <c r="F26" s="6"/>
-      <c r="G26" s="6"/>
+    <row r="25" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="B25" s="7"/>
+      <c r="C25" s="7"/>
+      <c r="D25" s="7"/>
+      <c r="E25" s="7"/>
+      <c r="F25" s="21"/>
+      <c r="G25" s="18" t="str">
+        <f aca="false">IF(F25="","",IF(UPPER(TRIM(F25))="B","Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="B26" s="7"/>
+      <c r="C26" s="7"/>
+      <c r="D26" s="7"/>
+      <c r="E26" s="7"/>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="22"/>
+      <c r="B27" s="22"/>
+      <c r="C27" s="22"/>
+      <c r="D27" s="22"/>
+      <c r="E27" s="22"/>
+      <c r="F27" s="22"/>
+      <c r="G27" s="22"/>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="22"/>
+      <c r="B28" s="22"/>
+      <c r="C28" s="22"/>
+      <c r="D28" s="22"/>
+      <c r="E28" s="22"/>
+      <c r="F28" s="22"/>
+      <c r="G28" s="22"/>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="22"/>
+      <c r="B29" s="22"/>
+      <c r="C29" s="22"/>
+      <c r="D29" s="22"/>
+      <c r="E29" s="22"/>
+      <c r="F29" s="22"/>
+      <c r="G29" s="22"/>
+    </row>
+    <row r="30" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="B30" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="C30" s="20"/>
+      <c r="D30" s="20"/>
+      <c r="E30" s="20"/>
+      <c r="F30" s="20"/>
+      <c r="G30" s="20"/>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="23" t="s">
+        <v>47</v>
+      </c>
+      <c r="B33" s="23"/>
+      <c r="C33" s="23"/>
+      <c r="D33" s="23"/>
+      <c r="E33" s="23"/>
+      <c r="F33" s="23"/>
+      <c r="G33" s="23"/>
+    </row>
+    <row r="34" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="24" t="s">
+        <v>48</v>
+      </c>
+      <c r="B34" s="25" t="s">
+        <v>49</v>
+      </c>
+      <c r="C34" s="25"/>
+      <c r="D34" s="25"/>
+      <c r="E34" s="25"/>
+      <c r="F34" s="25"/>
+      <c r="G34" s="25"/>
+    </row>
+    <row r="35" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="24" t="s">
+        <v>50</v>
+      </c>
+      <c r="B35" s="25" t="s">
+        <v>51</v>
+      </c>
+      <c r="C35" s="25"/>
+      <c r="D35" s="25"/>
+      <c r="E35" s="25"/>
+      <c r="F35" s="25"/>
+      <c r="G35" s="25"/>
+    </row>
+    <row r="37" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="B37" s="6"/>
+      <c r="C37" s="6"/>
+      <c r="D37" s="6"/>
+      <c r="E37" s="6"/>
+      <c r="F37" s="6"/>
+      <c r="G37" s="6"/>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="B38" s="6"/>
+      <c r="C38" s="6"/>
+      <c r="D38" s="6"/>
+      <c r="E38" s="6"/>
+      <c r="F38" s="6"/>
+      <c r="G38" s="6"/>
     </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="19">
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="A13:G13"/>
     <mergeCell ref="A15:E15"/>
     <mergeCell ref="A16:E16"/>
-    <mergeCell ref="A17:E17"/>
-    <mergeCell ref="A18:E18"/>
+    <mergeCell ref="B17:G17"/>
     <mergeCell ref="A19:E19"/>
-    <mergeCell ref="A20:E20"/>
-    <mergeCell ref="A21:G23"/>
-    <mergeCell ref="A25:G25"/>
-    <mergeCell ref="A26:G26"/>
+    <mergeCell ref="B20:G20"/>
+    <mergeCell ref="A22:E22"/>
+    <mergeCell ref="B23:G23"/>
+    <mergeCell ref="A25:E25"/>
+    <mergeCell ref="A26:E26"/>
+    <mergeCell ref="A27:G29"/>
+    <mergeCell ref="B30:G30"/>
+    <mergeCell ref="A33:G33"/>
+    <mergeCell ref="B34:G34"/>
+    <mergeCell ref="B35:G35"/>
+    <mergeCell ref="A37:G37"/>
+    <mergeCell ref="A38:G38"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -1290,7 +1548,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:G32"/>
+  <dimension ref="A1:G44"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34"/>
@@ -1301,7 +1559,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>44</v>
+        <v>54</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1311,7 +1569,7 @@
     </row>
     <row r="4" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="B4" s="6"/>
       <c r="C4" s="6"/>
@@ -1322,7 +1580,7 @@
     </row>
     <row r="5" customFormat="false" ht="78.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="B5" s="7"/>
       <c r="C5" s="7"/>
@@ -1333,10 +1591,10 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="17" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="C7" s="17"/>
       <c r="D7" s="17"/>
@@ -1345,11 +1603,11 @@
       <c r="G7" s="17"/>
     </row>
     <row r="8" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="21" t="s">
-        <v>49</v>
+      <c r="A8" s="26" t="s">
+        <v>59</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="C8" s="7"/>
       <c r="D8" s="7"/>
@@ -1358,11 +1616,11 @@
       <c r="G8" s="7"/>
     </row>
     <row r="9" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="21" t="s">
-        <v>51</v>
+      <c r="A9" s="26" t="s">
+        <v>61</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
@@ -1371,11 +1629,11 @@
       <c r="G9" s="7"/>
     </row>
     <row r="10" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="21" t="s">
-        <v>53</v>
+      <c r="A10" s="26" t="s">
+        <v>63</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="C10" s="7"/>
       <c r="D10" s="7"/>
@@ -1384,11 +1642,11 @@
       <c r="G10" s="7"/>
     </row>
     <row r="11" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="21" t="s">
-        <v>55</v>
+      <c r="A11" s="26" t="s">
+        <v>65</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="C11" s="7"/>
       <c r="D11" s="7"/>
@@ -1397,11 +1655,11 @@
       <c r="G11" s="7"/>
     </row>
     <row r="12" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="21" t="s">
-        <v>57</v>
+      <c r="A12" s="26" t="s">
+        <v>67</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="C12" s="7"/>
       <c r="D12" s="7"/>
@@ -1410,11 +1668,11 @@
       <c r="G12" s="7"/>
     </row>
     <row r="13" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="21" t="s">
-        <v>59</v>
+      <c r="A13" s="26" t="s">
+        <v>69</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="C13" s="7"/>
       <c r="D13" s="7"/>
@@ -1439,7 +1697,7 @@
     </row>
     <row r="16" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="7" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="B16" s="7"/>
       <c r="C16" s="7"/>
@@ -1451,187 +1709,276 @@
         <v/>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="B17" s="7"/>
-      <c r="C17" s="7"/>
-      <c r="D17" s="7"/>
-      <c r="E17" s="7"/>
-      <c r="F17" s="12"/>
-      <c r="G17" s="18" t="str">
-        <f aca="false">IF(F17="","",IF(ABS(F17-(176))&lt;=1,"Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="B18" s="7"/>
-      <c r="C18" s="7"/>
-      <c r="D18" s="7"/>
-      <c r="E18" s="7"/>
-      <c r="F18" s="12"/>
-      <c r="G18" s="18" t="str">
-        <f aca="false">IF(F18="","",IF(ABS(F18-(206))&lt;=1,"Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
+    <row r="17" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="B17" s="20" t="s">
+        <v>72</v>
+      </c>
+      <c r="C17" s="20"/>
+      <c r="D17" s="20"/>
+      <c r="E17" s="20"/>
+      <c r="F17" s="20"/>
+      <c r="G17" s="20"/>
     </row>
     <row r="19" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="7" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="B19" s="7"/>
       <c r="C19" s="7"/>
       <c r="D19" s="7"/>
       <c r="E19" s="7"/>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="B20" s="7"/>
-      <c r="C20" s="7"/>
-      <c r="D20" s="7"/>
-      <c r="E20" s="7"/>
-      <c r="F20" s="19"/>
-      <c r="G20" s="18" t="str">
-        <f aca="false">IF(F20="","",IF(UPPER(TRIM(F20))="JA","Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="B21" s="7"/>
-      <c r="C21" s="7"/>
-      <c r="D21" s="7"/>
-      <c r="E21" s="7"/>
-      <c r="F21" s="19"/>
-      <c r="G21" s="18" t="str">
-        <f aca="false">IF(F21="","",IF(UPPER(TRIM(F21))="NEI","Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="F19" s="12"/>
+      <c r="G19" s="18" t="str">
+        <f aca="false">IF(F19="","",IF(ABS(F19-(176))&lt;=1,"Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="B20" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="C20" s="20"/>
+      <c r="D20" s="20"/>
+      <c r="E20" s="20"/>
+      <c r="F20" s="20"/>
+      <c r="G20" s="20"/>
+    </row>
+    <row r="22" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="7" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="B22" s="7"/>
       <c r="C22" s="7"/>
       <c r="D22" s="7"/>
       <c r="E22" s="7"/>
-      <c r="F22" s="19"/>
+      <c r="F22" s="12"/>
       <c r="G22" s="18" t="str">
-        <f aca="false">IF(F22="","",IF(UPPER(TRIM(F22))="JA","Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="B23" s="7"/>
-      <c r="C23" s="7"/>
-      <c r="D23" s="7"/>
-      <c r="E23" s="7"/>
-      <c r="F23" s="19"/>
-      <c r="G23" s="18" t="str">
-        <f aca="false">IF(F23="","",IF(UPPER(TRIM(F23))="JA","Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="B24" s="7"/>
-      <c r="C24" s="7"/>
-      <c r="D24" s="7"/>
-      <c r="E24" s="7"/>
-      <c r="F24" s="19"/>
-      <c r="G24" s="18" t="str">
-        <f aca="false">IF(F24="","",IF(UPPER(TRIM(F24))="JA","Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <f aca="false">IF(F22="","",IF(ABS(F22-(206))&lt;=1,"Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="B23" s="20" t="s">
+        <v>76</v>
+      </c>
+      <c r="C23" s="20"/>
+      <c r="D23" s="20"/>
+      <c r="E23" s="20"/>
+      <c r="F23" s="20"/>
+      <c r="G23" s="20"/>
+    </row>
+    <row r="25" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="7" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="B25" s="7"/>
       <c r="C25" s="7"/>
       <c r="D25" s="7"/>
       <c r="E25" s="7"/>
-      <c r="F25" s="19"/>
-      <c r="G25" s="18" t="str">
-        <f aca="false">IF(F25="","",IF(UPPER(TRIM(F25))="JA","Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="7" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="B26" s="7"/>
       <c r="C26" s="7"/>
       <c r="D26" s="7"/>
       <c r="E26" s="7"/>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="20"/>
-      <c r="B27" s="20"/>
-      <c r="C27" s="20"/>
-      <c r="D27" s="20"/>
-      <c r="E27" s="20"/>
-      <c r="F27" s="20"/>
-      <c r="G27" s="20"/>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="20"/>
-      <c r="B28" s="20"/>
-      <c r="C28" s="20"/>
-      <c r="D28" s="20"/>
-      <c r="E28" s="20"/>
-      <c r="F28" s="20"/>
-      <c r="G28" s="20"/>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="20"/>
-      <c r="B29" s="20"/>
-      <c r="C29" s="20"/>
-      <c r="D29" s="20"/>
-      <c r="E29" s="20"/>
-      <c r="F29" s="20"/>
-      <c r="G29" s="20"/>
-    </row>
-    <row r="31" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="B31" s="6"/>
-      <c r="C31" s="6"/>
-      <c r="D31" s="6"/>
-      <c r="E31" s="6"/>
-      <c r="F31" s="6"/>
-      <c r="G31" s="6"/>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B32" s="6"/>
-      <c r="C32" s="6"/>
-      <c r="D32" s="6"/>
-      <c r="E32" s="6"/>
-      <c r="F32" s="6"/>
-      <c r="G32" s="6"/>
+      <c r="F26" s="21"/>
+      <c r="G26" s="18" t="str">
+        <f aca="false">IF(F26="","",IF(UPPER(TRIM(F26))="JA","Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="B27" s="7"/>
+      <c r="C27" s="7"/>
+      <c r="D27" s="7"/>
+      <c r="E27" s="7"/>
+      <c r="F27" s="21"/>
+      <c r="G27" s="18" t="str">
+        <f aca="false">IF(F27="","",IF(UPPER(TRIM(F27))="NEI","Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="B28" s="7"/>
+      <c r="C28" s="7"/>
+      <c r="D28" s="7"/>
+      <c r="E28" s="7"/>
+      <c r="F28" s="21"/>
+      <c r="G28" s="18" t="str">
+        <f aca="false">IF(F28="","",IF(UPPER(TRIM(F28))="JA","Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="B29" s="7"/>
+      <c r="C29" s="7"/>
+      <c r="D29" s="7"/>
+      <c r="E29" s="7"/>
+      <c r="F29" s="21"/>
+      <c r="G29" s="18" t="str">
+        <f aca="false">IF(F29="","",IF(UPPER(TRIM(F29))="JA","Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="B30" s="7"/>
+      <c r="C30" s="7"/>
+      <c r="D30" s="7"/>
+      <c r="E30" s="7"/>
+      <c r="F30" s="21"/>
+      <c r="G30" s="18" t="str">
+        <f aca="false">IF(F30="","",IF(UPPER(TRIM(F30))="JA","Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="B31" s="7"/>
+      <c r="C31" s="7"/>
+      <c r="D31" s="7"/>
+      <c r="E31" s="7"/>
+      <c r="F31" s="21"/>
+      <c r="G31" s="18" t="str">
+        <f aca="false">IF(F31="","",IF(UPPER(TRIM(F31))="JA","Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="B32" s="7"/>
+      <c r="C32" s="7"/>
+      <c r="D32" s="7"/>
+      <c r="E32" s="7"/>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="22"/>
+      <c r="B33" s="22"/>
+      <c r="C33" s="22"/>
+      <c r="D33" s="22"/>
+      <c r="E33" s="22"/>
+      <c r="F33" s="22"/>
+      <c r="G33" s="22"/>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="22"/>
+      <c r="B34" s="22"/>
+      <c r="C34" s="22"/>
+      <c r="D34" s="22"/>
+      <c r="E34" s="22"/>
+      <c r="F34" s="22"/>
+      <c r="G34" s="22"/>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="22"/>
+      <c r="B35" s="22"/>
+      <c r="C35" s="22"/>
+      <c r="D35" s="22"/>
+      <c r="E35" s="22"/>
+      <c r="F35" s="22"/>
+      <c r="G35" s="22"/>
+    </row>
+    <row r="36" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="B36" s="20" t="s">
+        <v>85</v>
+      </c>
+      <c r="C36" s="20"/>
+      <c r="D36" s="20"/>
+      <c r="E36" s="20"/>
+      <c r="F36" s="20"/>
+      <c r="G36" s="20"/>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="23" t="s">
+        <v>47</v>
+      </c>
+      <c r="B39" s="23"/>
+      <c r="C39" s="23"/>
+      <c r="D39" s="23"/>
+      <c r="E39" s="23"/>
+      <c r="F39" s="23"/>
+      <c r="G39" s="23"/>
+    </row>
+    <row r="40" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="24" t="s">
+        <v>86</v>
+      </c>
+      <c r="B40" s="25" t="s">
+        <v>87</v>
+      </c>
+      <c r="C40" s="25"/>
+      <c r="D40" s="25"/>
+      <c r="E40" s="25"/>
+      <c r="F40" s="25"/>
+      <c r="G40" s="25"/>
+    </row>
+    <row r="41" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="24" t="s">
+        <v>88</v>
+      </c>
+      <c r="B41" s="25" t="s">
+        <v>89</v>
+      </c>
+      <c r="C41" s="25"/>
+      <c r="D41" s="25"/>
+      <c r="E41" s="25"/>
+      <c r="F41" s="25"/>
+      <c r="G41" s="25"/>
+    </row>
+    <row r="43" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="B43" s="6"/>
+      <c r="C43" s="6"/>
+      <c r="D43" s="6"/>
+      <c r="E43" s="6"/>
+      <c r="F43" s="6"/>
+      <c r="G43" s="6"/>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="B44" s="6"/>
+      <c r="C44" s="6"/>
+      <c r="D44" s="6"/>
+      <c r="E44" s="6"/>
+      <c r="F44" s="6"/>
+      <c r="G44" s="6"/>
     </row>
   </sheetData>
-  <mergeCells count="24">
+  <mergeCells count="31">
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="B7:G7"/>
@@ -1643,19 +1990,26 @@
     <mergeCell ref="B13:G13"/>
     <mergeCell ref="A15:E15"/>
     <mergeCell ref="A16:E16"/>
-    <mergeCell ref="A17:E17"/>
-    <mergeCell ref="A18:E18"/>
+    <mergeCell ref="B17:G17"/>
     <mergeCell ref="A19:E19"/>
-    <mergeCell ref="A20:E20"/>
-    <mergeCell ref="A21:E21"/>
+    <mergeCell ref="B20:G20"/>
     <mergeCell ref="A22:E22"/>
-    <mergeCell ref="A23:E23"/>
-    <mergeCell ref="A24:E24"/>
+    <mergeCell ref="B23:G23"/>
     <mergeCell ref="A25:E25"/>
     <mergeCell ref="A26:E26"/>
-    <mergeCell ref="A27:G29"/>
-    <mergeCell ref="A31:G31"/>
-    <mergeCell ref="A32:G32"/>
+    <mergeCell ref="A27:E27"/>
+    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="A29:E29"/>
+    <mergeCell ref="A30:E30"/>
+    <mergeCell ref="A31:E31"/>
+    <mergeCell ref="A32:E32"/>
+    <mergeCell ref="A33:G35"/>
+    <mergeCell ref="B36:G36"/>
+    <mergeCell ref="A39:G39"/>
+    <mergeCell ref="B40:G40"/>
+    <mergeCell ref="B41:G41"/>
+    <mergeCell ref="A43:G43"/>
+    <mergeCell ref="A44:G44"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -1672,7 +2026,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:G32"/>
+  <dimension ref="A1:G44"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34"/>
@@ -1683,7 +2037,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>73</v>
+        <v>91</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1693,7 +2047,7 @@
     </row>
     <row r="4" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="B4" s="6"/>
       <c r="C4" s="6"/>
@@ -1704,7 +2058,7 @@
     </row>
     <row r="5" customFormat="false" ht="78.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="B5" s="7"/>
       <c r="C5" s="7"/>
@@ -1715,21 +2069,21 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="s">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>78</v>
+        <v>96</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="B8" s="22" t="s">
-        <v>80</v>
+        <v>97</v>
+      </c>
+      <c r="B8" s="27" t="s">
+        <v>98</v>
       </c>
       <c r="C8" s="11" t="n">
         <v>6500</v>
@@ -1737,10 +2091,10 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="13" t="s">
-        <v>81</v>
-      </c>
-      <c r="B9" s="23" t="s">
-        <v>82</v>
+        <v>99</v>
+      </c>
+      <c r="B9" s="28" t="s">
+        <v>100</v>
       </c>
       <c r="C9" s="14" t="n">
         <v>640</v>
@@ -1748,10 +2102,10 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="10" t="s">
-        <v>83</v>
-      </c>
-      <c r="B10" s="22" t="s">
-        <v>84</v>
+        <v>101</v>
+      </c>
+      <c r="B10" s="27" t="s">
+        <v>102</v>
       </c>
       <c r="C10" s="11" t="n">
         <v>800</v>
@@ -1759,10 +2113,10 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="13" t="s">
-        <v>85</v>
-      </c>
-      <c r="B11" s="23" t="s">
-        <v>82</v>
+        <v>103</v>
+      </c>
+      <c r="B11" s="28" t="s">
+        <v>100</v>
       </c>
       <c r="C11" s="14" t="n">
         <v>267</v>
@@ -1770,10 +2124,10 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="10" t="s">
-        <v>86</v>
-      </c>
-      <c r="B12" s="22" t="s">
-        <v>80</v>
+        <v>104</v>
+      </c>
+      <c r="B12" s="27" t="s">
+        <v>98</v>
       </c>
       <c r="C12" s="11" t="n">
         <v>8830</v>
@@ -1807,7 +2161,7 @@
     </row>
     <row r="16" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="7" t="s">
-        <v>87</v>
+        <v>105</v>
       </c>
       <c r="B16" s="7"/>
       <c r="C16" s="7"/>
@@ -1819,205 +2173,301 @@
         <v/>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="B17" s="7"/>
-      <c r="C17" s="7"/>
-      <c r="D17" s="7"/>
-      <c r="E17" s="7"/>
-      <c r="F17" s="12"/>
-      <c r="G17" s="18" t="str">
-        <f aca="false">IF(F17="","",IF(ABS(F17-(50684))&lt;=0.000000001,"Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="B18" s="7"/>
-      <c r="C18" s="7"/>
-      <c r="D18" s="7"/>
-      <c r="E18" s="7"/>
-      <c r="F18" s="12"/>
-      <c r="G18" s="18" t="str">
-        <f aca="false">IF(F18="","",IF(ABS(F18-(2296))&lt;=0.000000001,"Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
+    <row r="17" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="B17" s="20" t="s">
+        <v>106</v>
+      </c>
+      <c r="C17" s="20"/>
+      <c r="D17" s="20"/>
+      <c r="E17" s="20"/>
+      <c r="F17" s="20"/>
+      <c r="G17" s="20"/>
     </row>
     <row r="19" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="7" t="s">
-        <v>90</v>
+        <v>107</v>
       </c>
       <c r="B19" s="7"/>
       <c r="C19" s="7"/>
       <c r="D19" s="7"/>
       <c r="E19" s="7"/>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="B20" s="7"/>
-      <c r="C20" s="7"/>
-      <c r="D20" s="7"/>
-      <c r="E20" s="7"/>
-      <c r="F20" s="19"/>
-      <c r="G20" s="18" t="str">
-        <f aca="false">IF(F20="","",IF(UPPER(TRIM(F20))="JA","Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="7" t="s">
-        <v>92</v>
-      </c>
-      <c r="B21" s="7"/>
-      <c r="C21" s="7"/>
-      <c r="D21" s="7"/>
-      <c r="E21" s="7"/>
-      <c r="F21" s="19"/>
-      <c r="G21" s="18" t="str">
-        <f aca="false">IF(F21="","",IF(UPPER(TRIM(F21))="JA","Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="F19" s="12"/>
+      <c r="G19" s="18" t="str">
+        <f aca="false">IF(F19="","",IF(ABS(F19-(50684))&lt;=0.000000001,"Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="B20" s="20" t="s">
+        <v>108</v>
+      </c>
+      <c r="C20" s="20"/>
+      <c r="D20" s="20"/>
+      <c r="E20" s="20"/>
+      <c r="F20" s="20"/>
+      <c r="G20" s="20"/>
+    </row>
+    <row r="22" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="7" t="s">
-        <v>93</v>
+        <v>109</v>
       </c>
       <c r="B22" s="7"/>
       <c r="C22" s="7"/>
       <c r="D22" s="7"/>
       <c r="E22" s="7"/>
-      <c r="F22" s="19"/>
+      <c r="F22" s="12"/>
       <c r="G22" s="18" t="str">
-        <f aca="false">IF(F22="","",IF(UPPER(TRIM(F22))="JA","Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="B23" s="7"/>
-      <c r="C23" s="7"/>
-      <c r="D23" s="7"/>
-      <c r="E23" s="7"/>
-      <c r="F23" s="19"/>
-      <c r="G23" s="18" t="str">
-        <f aca="false">IF(F23="","",IF(UPPER(TRIM(F23))="NEI","Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="7" t="s">
-        <v>95</v>
-      </c>
-      <c r="B24" s="7"/>
-      <c r="C24" s="7"/>
-      <c r="D24" s="7"/>
-      <c r="E24" s="7"/>
-      <c r="F24" s="19"/>
-      <c r="G24" s="18" t="str">
-        <f aca="false">IF(F24="","",IF(UPPER(TRIM(F24))="NEI","Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <f aca="false">IF(F22="","",IF(ABS(F22-(2296))&lt;=0.000000001,"Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="B23" s="20" t="s">
+        <v>110</v>
+      </c>
+      <c r="C23" s="20"/>
+      <c r="D23" s="20"/>
+      <c r="E23" s="20"/>
+      <c r="F23" s="20"/>
+      <c r="G23" s="20"/>
+    </row>
+    <row r="25" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="7" t="s">
-        <v>96</v>
+        <v>111</v>
       </c>
       <c r="B25" s="7"/>
       <c r="C25" s="7"/>
       <c r="D25" s="7"/>
       <c r="E25" s="7"/>
-      <c r="F25" s="19"/>
-      <c r="G25" s="18" t="str">
-        <f aca="false">IF(F25="","",IF(UPPER(TRIM(F25))="NEI","Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="7" t="s">
-        <v>97</v>
+        <v>112</v>
       </c>
       <c r="B26" s="7"/>
       <c r="C26" s="7"/>
       <c r="D26" s="7"/>
       <c r="E26" s="7"/>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="20"/>
-      <c r="B27" s="20"/>
-      <c r="C27" s="20"/>
-      <c r="D27" s="20"/>
-      <c r="E27" s="20"/>
-      <c r="F27" s="20"/>
-      <c r="G27" s="20"/>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="20"/>
-      <c r="B28" s="20"/>
-      <c r="C28" s="20"/>
-      <c r="D28" s="20"/>
-      <c r="E28" s="20"/>
-      <c r="F28" s="20"/>
-      <c r="G28" s="20"/>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="20"/>
-      <c r="B29" s="20"/>
-      <c r="C29" s="20"/>
-      <c r="D29" s="20"/>
-      <c r="E29" s="20"/>
-      <c r="F29" s="20"/>
-      <c r="G29" s="20"/>
-    </row>
-    <row r="31" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="B31" s="6"/>
-      <c r="C31" s="6"/>
-      <c r="D31" s="6"/>
-      <c r="E31" s="6"/>
-      <c r="F31" s="6"/>
-      <c r="G31" s="6"/>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B32" s="6"/>
-      <c r="C32" s="6"/>
-      <c r="D32" s="6"/>
-      <c r="E32" s="6"/>
-      <c r="F32" s="6"/>
-      <c r="G32" s="6"/>
+      <c r="F26" s="21"/>
+      <c r="G26" s="18" t="str">
+        <f aca="false">IF(F26="","",IF(UPPER(TRIM(F26))="JA","Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="B27" s="7"/>
+      <c r="C27" s="7"/>
+      <c r="D27" s="7"/>
+      <c r="E27" s="7"/>
+      <c r="F27" s="21"/>
+      <c r="G27" s="18" t="str">
+        <f aca="false">IF(F27="","",IF(UPPER(TRIM(F27))="JA","Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="B28" s="7"/>
+      <c r="C28" s="7"/>
+      <c r="D28" s="7"/>
+      <c r="E28" s="7"/>
+      <c r="F28" s="21"/>
+      <c r="G28" s="18" t="str">
+        <f aca="false">IF(F28="","",IF(UPPER(TRIM(F28))="JA","Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="B29" s="7"/>
+      <c r="C29" s="7"/>
+      <c r="D29" s="7"/>
+      <c r="E29" s="7"/>
+      <c r="F29" s="21"/>
+      <c r="G29" s="18" t="str">
+        <f aca="false">IF(F29="","",IF(UPPER(TRIM(F29))="NEI","Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="B30" s="7"/>
+      <c r="C30" s="7"/>
+      <c r="D30" s="7"/>
+      <c r="E30" s="7"/>
+      <c r="F30" s="21"/>
+      <c r="G30" s="18" t="str">
+        <f aca="false">IF(F30="","",IF(UPPER(TRIM(F30))="NEI","Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="B31" s="7"/>
+      <c r="C31" s="7"/>
+      <c r="D31" s="7"/>
+      <c r="E31" s="7"/>
+      <c r="F31" s="21"/>
+      <c r="G31" s="18" t="str">
+        <f aca="false">IF(F31="","",IF(UPPER(TRIM(F31))="NEI","Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="B32" s="7"/>
+      <c r="C32" s="7"/>
+      <c r="D32" s="7"/>
+      <c r="E32" s="7"/>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="22"/>
+      <c r="B33" s="22"/>
+      <c r="C33" s="22"/>
+      <c r="D33" s="22"/>
+      <c r="E33" s="22"/>
+      <c r="F33" s="22"/>
+      <c r="G33" s="22"/>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="22"/>
+      <c r="B34" s="22"/>
+      <c r="C34" s="22"/>
+      <c r="D34" s="22"/>
+      <c r="E34" s="22"/>
+      <c r="F34" s="22"/>
+      <c r="G34" s="22"/>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="22"/>
+      <c r="B35" s="22"/>
+      <c r="C35" s="22"/>
+      <c r="D35" s="22"/>
+      <c r="E35" s="22"/>
+      <c r="F35" s="22"/>
+      <c r="G35" s="22"/>
+    </row>
+    <row r="36" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="B36" s="20" t="s">
+        <v>119</v>
+      </c>
+      <c r="C36" s="20"/>
+      <c r="D36" s="20"/>
+      <c r="E36" s="20"/>
+      <c r="F36" s="20"/>
+      <c r="G36" s="20"/>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="23" t="s">
+        <v>47</v>
+      </c>
+      <c r="B39" s="23"/>
+      <c r="C39" s="23"/>
+      <c r="D39" s="23"/>
+      <c r="E39" s="23"/>
+      <c r="F39" s="23"/>
+      <c r="G39" s="23"/>
+    </row>
+    <row r="40" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="24" t="s">
+        <v>120</v>
+      </c>
+      <c r="B40" s="25" t="s">
+        <v>121</v>
+      </c>
+      <c r="C40" s="25"/>
+      <c r="D40" s="25"/>
+      <c r="E40" s="25"/>
+      <c r="F40" s="25"/>
+      <c r="G40" s="25"/>
+    </row>
+    <row r="41" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="24" t="s">
+        <v>122</v>
+      </c>
+      <c r="B41" s="25" t="s">
+        <v>123</v>
+      </c>
+      <c r="C41" s="25"/>
+      <c r="D41" s="25"/>
+      <c r="E41" s="25"/>
+      <c r="F41" s="25"/>
+      <c r="G41" s="25"/>
+    </row>
+    <row r="43" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="B43" s="6"/>
+      <c r="C43" s="6"/>
+      <c r="D43" s="6"/>
+      <c r="E43" s="6"/>
+      <c r="F43" s="6"/>
+      <c r="G43" s="6"/>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="B44" s="6"/>
+      <c r="C44" s="6"/>
+      <c r="D44" s="6"/>
+      <c r="E44" s="6"/>
+      <c r="F44" s="6"/>
+      <c r="G44" s="6"/>
     </row>
   </sheetData>
-  <mergeCells count="18">
+  <mergeCells count="25">
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="A13:G13"/>
     <mergeCell ref="A15:E15"/>
     <mergeCell ref="A16:E16"/>
-    <mergeCell ref="A17:E17"/>
-    <mergeCell ref="A18:E18"/>
+    <mergeCell ref="B17:G17"/>
     <mergeCell ref="A19:E19"/>
-    <mergeCell ref="A20:E20"/>
-    <mergeCell ref="A21:E21"/>
+    <mergeCell ref="B20:G20"/>
     <mergeCell ref="A22:E22"/>
-    <mergeCell ref="A23:E23"/>
-    <mergeCell ref="A24:E24"/>
+    <mergeCell ref="B23:G23"/>
     <mergeCell ref="A25:E25"/>
     <mergeCell ref="A26:E26"/>
-    <mergeCell ref="A27:G29"/>
-    <mergeCell ref="A31:G31"/>
-    <mergeCell ref="A32:G32"/>
+    <mergeCell ref="A27:E27"/>
+    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="A29:E29"/>
+    <mergeCell ref="A30:E30"/>
+    <mergeCell ref="A31:E31"/>
+    <mergeCell ref="A32:E32"/>
+    <mergeCell ref="A33:G35"/>
+    <mergeCell ref="B36:G36"/>
+    <mergeCell ref="A39:G39"/>
+    <mergeCell ref="B40:G40"/>
+    <mergeCell ref="B41:G41"/>
+    <mergeCell ref="A43:G43"/>
+    <mergeCell ref="A44:G44"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -2034,7 +2484,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:G31"/>
+  <dimension ref="A1:G43"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34"/>
@@ -2045,7 +2495,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>99</v>
+        <v>125</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2055,7 +2505,7 @@
     </row>
     <row r="4" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>100</v>
+        <v>126</v>
       </c>
       <c r="B4" s="6"/>
       <c r="C4" s="6"/>
@@ -2066,7 +2516,7 @@
     </row>
     <row r="5" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>101</v>
+        <v>127</v>
       </c>
       <c r="B5" s="7"/>
       <c r="C5" s="7"/>
@@ -2077,10 +2527,10 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="17" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="C7" s="17"/>
       <c r="D7" s="17"/>
@@ -2089,11 +2539,11 @@
       <c r="G7" s="17"/>
     </row>
     <row r="8" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="21" t="s">
-        <v>102</v>
+      <c r="A8" s="26" t="s">
+        <v>128</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>103</v>
+        <v>129</v>
       </c>
       <c r="C8" s="7"/>
       <c r="D8" s="7"/>
@@ -2102,11 +2552,11 @@
       <c r="G8" s="7"/>
     </row>
     <row r="9" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="21" t="s">
-        <v>104</v>
+      <c r="A9" s="26" t="s">
+        <v>130</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>105</v>
+        <v>131</v>
       </c>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
@@ -2115,11 +2565,11 @@
       <c r="G9" s="7"/>
     </row>
     <row r="10" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="21" t="s">
-        <v>106</v>
+      <c r="A10" s="26" t="s">
+        <v>132</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>107</v>
+        <v>133</v>
       </c>
       <c r="C10" s="7"/>
       <c r="D10" s="7"/>
@@ -2128,11 +2578,11 @@
       <c r="G10" s="7"/>
     </row>
     <row r="11" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="21" t="s">
-        <v>108</v>
+      <c r="A11" s="26" t="s">
+        <v>134</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>109</v>
+        <v>135</v>
       </c>
       <c r="C11" s="7"/>
       <c r="D11" s="7"/>
@@ -2141,11 +2591,11 @@
       <c r="G11" s="7"/>
     </row>
     <row r="12" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="21" t="s">
-        <v>110</v>
+      <c r="A12" s="26" t="s">
+        <v>136</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>111</v>
+        <v>137</v>
       </c>
       <c r="C12" s="7"/>
       <c r="D12" s="7"/>
@@ -2170,7 +2620,7 @@
     </row>
     <row r="15" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="7" t="s">
-        <v>112</v>
+        <v>138</v>
       </c>
       <c r="B15" s="7"/>
       <c r="C15" s="7"/>
@@ -2182,187 +2632,276 @@
         <v/>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="B16" s="7"/>
-      <c r="C16" s="7"/>
-      <c r="D16" s="7"/>
-      <c r="E16" s="7"/>
-      <c r="F16" s="12"/>
-      <c r="G16" s="18" t="str">
-        <f aca="false">IF(F16="","",IF(ABS(F16-(836640))&lt;=0.000000001,"Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="7" t="s">
-        <v>114</v>
-      </c>
-      <c r="B17" s="7"/>
-      <c r="C17" s="7"/>
-      <c r="D17" s="7"/>
-      <c r="E17" s="7"/>
-      <c r="F17" s="12"/>
-      <c r="G17" s="18" t="str">
-        <f aca="false">IF(F17="","",IF(ABS(F17-(784000))&lt;=0.000000001,"Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="B16" s="20" t="s">
+        <v>139</v>
+      </c>
+      <c r="C16" s="20"/>
+      <c r="D16" s="20"/>
+      <c r="E16" s="20"/>
+      <c r="F16" s="20"/>
+      <c r="G16" s="20"/>
+    </row>
+    <row r="18" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="7" t="s">
-        <v>115</v>
+        <v>140</v>
       </c>
       <c r="B18" s="7"/>
       <c r="C18" s="7"/>
       <c r="D18" s="7"/>
       <c r="E18" s="7"/>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="7" t="s">
-        <v>116</v>
-      </c>
-      <c r="B19" s="7"/>
-      <c r="C19" s="7"/>
-      <c r="D19" s="7"/>
-      <c r="E19" s="7"/>
-      <c r="F19" s="19"/>
-      <c r="G19" s="18" t="str">
-        <f aca="false">IF(F19="","",IF(UPPER(TRIM(F19))="JA","Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="7" t="s">
-        <v>117</v>
-      </c>
-      <c r="B20" s="7"/>
-      <c r="C20" s="7"/>
-      <c r="D20" s="7"/>
-      <c r="E20" s="7"/>
-      <c r="F20" s="19"/>
-      <c r="G20" s="18" t="str">
-        <f aca="false">IF(F20="","",IF(UPPER(TRIM(F20))="JA","Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="F18" s="12"/>
+      <c r="G18" s="18" t="str">
+        <f aca="false">IF(F18="","",IF(ABS(F18-(836640))&lt;=0.000000001,"Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="B19" s="20" t="s">
+        <v>141</v>
+      </c>
+      <c r="C19" s="20"/>
+      <c r="D19" s="20"/>
+      <c r="E19" s="20"/>
+      <c r="F19" s="20"/>
+      <c r="G19" s="20"/>
+    </row>
+    <row r="21" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="7" t="s">
-        <v>118</v>
+        <v>142</v>
       </c>
       <c r="B21" s="7"/>
       <c r="C21" s="7"/>
       <c r="D21" s="7"/>
       <c r="E21" s="7"/>
-      <c r="F21" s="19"/>
+      <c r="F21" s="12"/>
       <c r="G21" s="18" t="str">
-        <f aca="false">IF(F21="","",IF(UPPER(TRIM(F21))="JA","Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="7" t="s">
-        <v>119</v>
-      </c>
-      <c r="B22" s="7"/>
-      <c r="C22" s="7"/>
-      <c r="D22" s="7"/>
-      <c r="E22" s="7"/>
-      <c r="F22" s="19"/>
-      <c r="G22" s="18" t="str">
-        <f aca="false">IF(F22="","",IF(UPPER(TRIM(F22))="JA","Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="7" t="s">
-        <v>120</v>
-      </c>
-      <c r="B23" s="7"/>
-      <c r="C23" s="7"/>
-      <c r="D23" s="7"/>
-      <c r="E23" s="7"/>
-      <c r="F23" s="19"/>
-      <c r="G23" s="18" t="str">
-        <f aca="false">IF(F23="","",IF(UPPER(TRIM(F23))="NEI","Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <f aca="false">IF(F21="","",IF(ABS(F21-(784000))&lt;=0.000000001,"Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="B22" s="20" t="s">
+        <v>143</v>
+      </c>
+      <c r="C22" s="20"/>
+      <c r="D22" s="20"/>
+      <c r="E22" s="20"/>
+      <c r="F22" s="20"/>
+      <c r="G22" s="20"/>
+    </row>
+    <row r="24" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="7" t="s">
-        <v>121</v>
+        <v>144</v>
       </c>
       <c r="B24" s="7"/>
       <c r="C24" s="7"/>
       <c r="D24" s="7"/>
       <c r="E24" s="7"/>
-      <c r="F24" s="19"/>
-      <c r="G24" s="18" t="str">
-        <f aca="false">IF(F24="","",IF(UPPER(TRIM(F24))="NEI","Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="7" t="s">
-        <v>122</v>
+        <v>145</v>
       </c>
       <c r="B25" s="7"/>
       <c r="C25" s="7"/>
       <c r="D25" s="7"/>
       <c r="E25" s="7"/>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="20"/>
-      <c r="B26" s="20"/>
-      <c r="C26" s="20"/>
-      <c r="D26" s="20"/>
-      <c r="E26" s="20"/>
-      <c r="F26" s="20"/>
-      <c r="G26" s="20"/>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="20"/>
-      <c r="B27" s="20"/>
-      <c r="C27" s="20"/>
-      <c r="D27" s="20"/>
-      <c r="E27" s="20"/>
-      <c r="F27" s="20"/>
-      <c r="G27" s="20"/>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="20"/>
-      <c r="B28" s="20"/>
-      <c r="C28" s="20"/>
-      <c r="D28" s="20"/>
-      <c r="E28" s="20"/>
-      <c r="F28" s="20"/>
-      <c r="G28" s="20"/>
-    </row>
-    <row r="30" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="6" t="s">
-        <v>123</v>
-      </c>
-      <c r="B30" s="6"/>
-      <c r="C30" s="6"/>
-      <c r="D30" s="6"/>
-      <c r="E30" s="6"/>
-      <c r="F30" s="6"/>
-      <c r="G30" s="6"/>
-    </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B31" s="6"/>
-      <c r="C31" s="6"/>
-      <c r="D31" s="6"/>
-      <c r="E31" s="6"/>
-      <c r="F31" s="6"/>
-      <c r="G31" s="6"/>
+      <c r="F25" s="21"/>
+      <c r="G25" s="18" t="str">
+        <f aca="false">IF(F25="","",IF(UPPER(TRIM(F25))="JA","Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="B26" s="7"/>
+      <c r="C26" s="7"/>
+      <c r="D26" s="7"/>
+      <c r="E26" s="7"/>
+      <c r="F26" s="21"/>
+      <c r="G26" s="18" t="str">
+        <f aca="false">IF(F26="","",IF(UPPER(TRIM(F26))="JA","Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="B27" s="7"/>
+      <c r="C27" s="7"/>
+      <c r="D27" s="7"/>
+      <c r="E27" s="7"/>
+      <c r="F27" s="21"/>
+      <c r="G27" s="18" t="str">
+        <f aca="false">IF(F27="","",IF(UPPER(TRIM(F27))="JA","Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="B28" s="7"/>
+      <c r="C28" s="7"/>
+      <c r="D28" s="7"/>
+      <c r="E28" s="7"/>
+      <c r="F28" s="21"/>
+      <c r="G28" s="18" t="str">
+        <f aca="false">IF(F28="","",IF(UPPER(TRIM(F28))="JA","Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="B29" s="7"/>
+      <c r="C29" s="7"/>
+      <c r="D29" s="7"/>
+      <c r="E29" s="7"/>
+      <c r="F29" s="21"/>
+      <c r="G29" s="18" t="str">
+        <f aca="false">IF(F29="","",IF(UPPER(TRIM(F29))="NEI","Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="B30" s="7"/>
+      <c r="C30" s="7"/>
+      <c r="D30" s="7"/>
+      <c r="E30" s="7"/>
+      <c r="F30" s="21"/>
+      <c r="G30" s="18" t="str">
+        <f aca="false">IF(F30="","",IF(UPPER(TRIM(F30))="NEI","Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="B31" s="7"/>
+      <c r="C31" s="7"/>
+      <c r="D31" s="7"/>
+      <c r="E31" s="7"/>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="22"/>
+      <c r="B32" s="22"/>
+      <c r="C32" s="22"/>
+      <c r="D32" s="22"/>
+      <c r="E32" s="22"/>
+      <c r="F32" s="22"/>
+      <c r="G32" s="22"/>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="22"/>
+      <c r="B33" s="22"/>
+      <c r="C33" s="22"/>
+      <c r="D33" s="22"/>
+      <c r="E33" s="22"/>
+      <c r="F33" s="22"/>
+      <c r="G33" s="22"/>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="22"/>
+      <c r="B34" s="22"/>
+      <c r="C34" s="22"/>
+      <c r="D34" s="22"/>
+      <c r="E34" s="22"/>
+      <c r="F34" s="22"/>
+      <c r="G34" s="22"/>
+    </row>
+    <row r="35" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="B35" s="20" t="s">
+        <v>152</v>
+      </c>
+      <c r="C35" s="20"/>
+      <c r="D35" s="20"/>
+      <c r="E35" s="20"/>
+      <c r="F35" s="20"/>
+      <c r="G35" s="20"/>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="23" t="s">
+        <v>47</v>
+      </c>
+      <c r="B38" s="23"/>
+      <c r="C38" s="23"/>
+      <c r="D38" s="23"/>
+      <c r="E38" s="23"/>
+      <c r="F38" s="23"/>
+      <c r="G38" s="23"/>
+    </row>
+    <row r="39" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="24" t="s">
+        <v>153</v>
+      </c>
+      <c r="B39" s="25" t="s">
+        <v>154</v>
+      </c>
+      <c r="C39" s="25"/>
+      <c r="D39" s="25"/>
+      <c r="E39" s="25"/>
+      <c r="F39" s="25"/>
+      <c r="G39" s="25"/>
+    </row>
+    <row r="40" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="24" t="s">
+        <v>155</v>
+      </c>
+      <c r="B40" s="25" t="s">
+        <v>156</v>
+      </c>
+      <c r="C40" s="25"/>
+      <c r="D40" s="25"/>
+      <c r="E40" s="25"/>
+      <c r="F40" s="25"/>
+      <c r="G40" s="25"/>
+    </row>
+    <row r="42" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="B42" s="6"/>
+      <c r="C42" s="6"/>
+      <c r="D42" s="6"/>
+      <c r="E42" s="6"/>
+      <c r="F42" s="6"/>
+      <c r="G42" s="6"/>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="B43" s="6"/>
+      <c r="C43" s="6"/>
+      <c r="D43" s="6"/>
+      <c r="E43" s="6"/>
+      <c r="F43" s="6"/>
+      <c r="G43" s="6"/>
     </row>
   </sheetData>
-  <mergeCells count="23">
+  <mergeCells count="30">
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="B7:G7"/>
@@ -2373,19 +2912,26 @@
     <mergeCell ref="B12:G12"/>
     <mergeCell ref="A14:E14"/>
     <mergeCell ref="A15:E15"/>
-    <mergeCell ref="A16:E16"/>
-    <mergeCell ref="A17:E17"/>
+    <mergeCell ref="B16:G16"/>
     <mergeCell ref="A18:E18"/>
-    <mergeCell ref="A19:E19"/>
-    <mergeCell ref="A20:E20"/>
+    <mergeCell ref="B19:G19"/>
     <mergeCell ref="A21:E21"/>
-    <mergeCell ref="A22:E22"/>
-    <mergeCell ref="A23:E23"/>
+    <mergeCell ref="B22:G22"/>
     <mergeCell ref="A24:E24"/>
     <mergeCell ref="A25:E25"/>
-    <mergeCell ref="A26:G28"/>
-    <mergeCell ref="A30:G30"/>
-    <mergeCell ref="A31:G31"/>
+    <mergeCell ref="A26:E26"/>
+    <mergeCell ref="A27:E27"/>
+    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="A29:E29"/>
+    <mergeCell ref="A30:E30"/>
+    <mergeCell ref="A31:E31"/>
+    <mergeCell ref="A32:G34"/>
+    <mergeCell ref="B35:G35"/>
+    <mergeCell ref="A38:G38"/>
+    <mergeCell ref="B39:G39"/>
+    <mergeCell ref="B40:G40"/>
+    <mergeCell ref="A42:G42"/>
+    <mergeCell ref="A43:G43"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/pensum/ok02/OK02_Klasseoppgaver_v5.xlsx
+++ b/pensum/ok02/OK02_Klasseoppgaver_v5.xlsx
@@ -143,7 +143,7 @@
     <t xml:space="preserve">Formel og begrep</t>
   </si>
   <si>
-    <t xml:space="preserve">Varekostnad = varebeholdning (IB) + varekjøp − varebeholdning (UB) (Økonomistyring 2.2.1).</t>
+    <t xml:space="preserve">Varekostnad = varebeholdning ved start + varekjøp − varebeholdning ved slutt (Økonomistyring 2.2.1).</t>
   </si>
   <si>
     <t xml:space="preserve">b)  Hvor mye går ut av kontoen til Polarlys i april? Husk 30 dagers kreditt.</t>
@@ -305,7 +305,7 @@
     <t xml:space="preserve">Kort oppsummert: Direkte kostnader kan knyttes til et bestemt oppdrag (kalkyleobjektet): materiell, montørtimer og kjøring dit. Indirekte kostnader er felles for alle jobbene: husleie, administrasjon, strøm på verkstedet. Selvkost er direkte pluss jobbens andel av de indirekte. Fortjeneste er pris minus selvkost.</t>
   </si>
   <si>
-    <t xml:space="preserve">Borettslaget vil ha seks ladepunkter på parkeringsplassen. Hvert ladepunkt krever ladeboks og materiell for 6 500 kr og to montørtimer. Ida regner direkte lønnskostnad med en timesats på 640 kr, og kjøringen til borettslaget koster 800 kr. De indirekte kostnadene fordeler hun med 267 kr per montørtime (Nordlys' faste kostnader 3 840 000 delt på 14 400 fakturerte timer, avrundet). Prisen er 8 830 kr per ladepunkt uten mva. Gå fram slik: regn de direkte kostnadene, legg til den indirekte andelen, sammenlikn med prisen.</t>
+    <t xml:space="preserve">Borettslaget vil ha seks ladepunkter på parkeringsplassen. Hvert ladepunkt krever ladeboks og materiell for 6 500 kr og to montørtimer. Ida regner direkte lønnskostnad med en timesats på 640 kr, og kjøringen til borettslaget koster 800 kr. De indirekte kostnadene fordeler hun med 267 kr per montørtime (Nordlys' faste kostnader 3 840 000 delt på 14 400 fakturerte timer, avrundet). Prisen er 8 830 kr per ladepunkt uten merverdiavgift. Gå fram slik: regn de direkte kostnadene, legg til den indirekte andelen, sammenlikn med prisen.</t>
   </si>
   <si>
     <t xml:space="preserve">Post</t>
@@ -320,7 +320,7 @@
     <t xml:space="preserve">Ladeboks og materiell</t>
   </si>
   <si>
-    <t xml:space="preserve">6 stk</t>
+    <t xml:space="preserve">6 stykk</t>
   </si>
   <si>
     <t xml:space="preserve">Montørtimer (timesats)</t>
@@ -338,7 +338,7 @@
     <t xml:space="preserve">Indirekte, per montørtime</t>
   </si>
   <si>
-    <t xml:space="preserve">Pris til kunden, uten mva</t>
+    <t xml:space="preserve">Pris til kunden, uten merverdiavgift</t>
   </si>
   <si>
     <t xml:space="preserve">a)  Sum direkte kostnader for jobben, i kroner: materiell, montørtimer og kjøring.</t>
@@ -350,13 +350,13 @@
     <t xml:space="preserve">b)  Selvkosten for jobben, i kroner: direkte kostnader pluss den indirekte andelen, 267 kr per montørtime.</t>
   </si>
   <si>
-    <t xml:space="preserve">Selvkost (STK) = direkte kostnader + jobbens andel av de indirekte kostnadene (Økonomistyring 2.2.3 og 2.3). Fordelingen med sats per time kommer i kap. 5.</t>
+    <t xml:space="preserve">Selvkost = direkte kostnader + jobbens andel av de indirekte kostnadene (Økonomistyring 2.2.3 og 2.3). Fordelingen med sats per time kommer i kap. 5.</t>
   </si>
   <si>
     <t xml:space="preserve">c)  Fortjenesten på jobben, i kroner: salgsinntekt minus selvkost.</t>
   </si>
   <si>
-    <t xml:space="preserve">Fortjeneste = sum totale inntekter (STI) − sum totale kostnader (STK), og STI = P × M (Økonomistyring 2.3).</t>
+    <t xml:space="preserve">Fortjeneste = sum totale inntekter − sum totale kostnader, og salgsinntekt = pris × mengde (Økonomistyring 2.3).</t>
   </si>
   <si>
     <t xml:space="preserve">d)  Er dette en direkte kostnad for ladepunktjobben? Spør: kan kostnaden knyttes til akkurat denne jobben?</t>
@@ -398,7 +398,7 @@
     <t xml:space="preserve">Spør: kan kostnaden knyttes til akkurat denne jobben? Strømmen varierer med aktiviteten, men den kan ikke knyttes til borettslaget.</t>
   </si>
   <si>
-    <t xml:space="preserve">Kilde: Hjertnes, J. og Skorpen, K.: Økonomistyring for LØM-emnet, kap. 2, avsnitt 2.2.3 (direkte og indirekte kostnader, kalkyleobjekt, håndverksbedrift) og 2.3.1 (fortjeneste = STI − STK). Fordeling av indirekte kostnader: kap. 5. Nordlys Elektro AS er en konstruert casebedrift.</t>
+    <t xml:space="preserve">Kilde: Hjertnes, J. og Skorpen, K.: Økonomistyring for LØM-emnet, kap. 2, avsnitt 2.2.3 (direkte og indirekte kostnader, kalkyleobjekt, håndverksbedrift) og 2.3.1 (fortjeneste = sum totale inntekter − sum totale kostnader). Fordeling av indirekte kostnader: kap. 5. Nordlys Elektro AS er en konstruert casebedrift.</t>
   </si>
   <si>
     <t xml:space="preserve">B2 · Din egen el-bedrift: hva koster en montør?</t>
@@ -422,7 +422,7 @@
     <t xml:space="preserve">Bokas tabell 2.4: 46,8 % av lønn</t>
   </si>
   <si>
-    <t xml:space="preserve">Feriepenger inkl. aga</t>
+    <t xml:space="preserve">Feriepenger inkludert arbeidsgiveravgift</t>
   </si>
   <si>
     <t xml:space="preserve">13,7 % (12 % × 1,141). Fra 60 år: 14,3 % × 1,141 = 16,3 %</t>
@@ -431,7 +431,7 @@
     <t xml:space="preserve">Pensjon i tabellen</t>
   </si>
   <si>
-    <t xml:space="preserve">8,0 % + aga på pensjon 1,1 %. Minstekrav (OTP): 2 % + 0,3 %</t>
+    <t xml:space="preserve">8,0 % + arbeidsgiveravgift på pensjon 1,1 %. Lovens minstekrav: 2 % + 0,3 %</t>
   </si>
   <si>
     <t xml:space="preserve">Timer per montør</t>
@@ -455,7 +455,7 @@
     <t xml:space="preserve">c)  Fjell velger minstekravet for obligatorisk tjenestepensjon: 2 % pensjon og 0,3 % arbeidsgiveravgift på pensjon, i stedet for bokas 8,0 % og 1,1 %. Hva blir lønnskostnaden (montør under 60)?</t>
   </si>
   <si>
-    <t xml:space="preserve">Pensjonspremie minimum 2 % OTP (Økonomistyring 2.4.1; lov om obligatorisk tjenestepensjon § 4). Tabell 2.4 bruker 8,0 % pensjon og 1,1 % arbeidsgiveravgift på pensjon.</t>
+    <t xml:space="preserve">Pensjonspremie minimum 2 % (Økonomistyring 2.4.1; lov om obligatorisk tjenestepensjon § 4). Tabell 2.4 bruker 8,0 % pensjon og 1,1 % arbeidsgiveravgift på pensjon.</t>
   </si>
   <si>
     <t xml:space="preserve">d)  Hører dette med i de sosiale kostnadene på lønna (bokas tabell 2.4)?</t>
@@ -467,7 +467,7 @@
     <t xml:space="preserve">      Feriepenger   (Ja eller Nei)</t>
   </si>
   <si>
-    <t xml:space="preserve">      Pensjonspremie (OTP)   (Ja eller Nei)</t>
+    <t xml:space="preserve">      Pensjonspremie (obligatorisk tjenestepensjon)   (Ja eller Nei)</t>
   </si>
   <si>
     <t xml:space="preserve">      Sykepenger i arbeidsgiverperioden   (Ja eller Nei)</t>
@@ -1322,7 +1322,7 @@
         <v/>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="19" t="s">
         <v>38</v>
       </c>

--- a/pensum/ok02/OK02_Klasseoppgaver_v5.xlsx
+++ b/pensum/ok02/OK02_Klasseoppgaver_v5.xlsx
@@ -26,7 +26,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="158">
   <si>
-    <t xml:space="preserve">Klasseoppgaver til Økonomistyring kapittel 2: Viktige bedriftsøkonomiske begreper (V5)</t>
+    <t xml:space="preserve">Klasseoppgaver til Økonomistyring kapittel 2: Viktige bedriftsøkonomiske begreper (versjon 5)</t>
   </si>
   <si>
     <t xml:space="preserve">LØM · Fagskolen Oslo, Avdeling Elkraft · versjon 5, oktober 2026</t>
@@ -110,13 +110,13 @@
     <t xml:space="preserve">Mai</t>
   </si>
   <si>
-    <t xml:space="preserve">Lager ved starten (IB)</t>
+    <t xml:space="preserve">Inngående lager (lageret ved starten)</t>
   </si>
   <si>
     <t xml:space="preserve">+ Varekjøp (utgift)</t>
   </si>
   <si>
-    <t xml:space="preserve">− Lager ved slutten (UB)</t>
+    <t xml:space="preserve">− Utgående lager (lageret ved slutten)</t>
   </si>
   <si>
     <t xml:space="preserve">= Varekostnad</t>
@@ -1224,7 +1224,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="10" t="s">
         <v>28</v>
       </c>
@@ -1248,7 +1248,7 @@
         <v>520000</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="10" t="s">
         <v>30</v>
       </c>
